--- a/variant1.xlsx
+++ b/variant1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\omrmeroj_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313D2DF5-9BF0-48A0-AA36-9E34A6E92DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79801EDA-7404-486A-8E96-A5E48ACFB93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="131">
   <si>
     <t>T/r</t>
   </si>
@@ -413,6 +413,12 @@
   </si>
   <si>
     <t>1994-yil 21-oktabr</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>3.1</t>
   </si>
 </sst>
 </file>
@@ -490,12 +496,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1153,8 +1157,8 @@
       <c r="H12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I12" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1182,8 +1186,8 @@
       <c r="H13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I13" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1211,8 +1215,8 @@
       <c r="H14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I14" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1240,8 +1244,8 @@
       <c r="H15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I15" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1269,8 +1273,8 @@
       <c r="H16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I16" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1283,23 +1287,23 @@
       <c r="C17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>100</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>1000</v>
       </c>
       <c r="F17" s="4">
         <v>10000</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>10</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I17" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1327,8 +1331,8 @@
       <c r="H18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I18" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1356,8 +1360,8 @@
       <c r="H19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I19" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1385,8 +1389,8 @@
       <c r="H20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I20" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1414,8 +1418,8 @@
       <c r="H21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I21" s="4" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1443,8 +1447,8 @@
       <c r="H22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I22" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1472,8 +1476,8 @@
       <c r="H23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I23" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I23" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1501,8 +1505,8 @@
       <c r="H24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I24" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1530,8 +1534,8 @@
       <c r="H25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I25" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1559,8 +1563,8 @@
       <c r="H26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I26" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1588,8 +1592,8 @@
       <c r="H27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I27" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I27" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1617,8 +1621,8 @@
       <c r="H28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I28" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I28" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1646,8 +1650,8 @@
       <c r="H29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I29" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1675,38 +1679,907 @@
       <c r="H30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="4">
-        <v>1.1000000000000001</v>
+      <c r="I30" s="4" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I31">
-        <v>1.1000000000000001</v>
-      </c>
+      <c r="I31" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="5"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="5"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="5"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="5"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="5"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="5"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="5"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/variant1.xlsx
+++ b/variant1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\omrmeroj_backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79801EDA-7404-486A-8E96-A5E48ACFB93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64901E4D-848C-4155-A390-3F201D6283AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="129">
   <si>
     <t>T/r</t>
   </si>
@@ -413,12 +413,6 @@
   </si>
   <si>
     <t>1994-yil 21-oktabr</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>3.1</t>
   </si>
 </sst>
 </file>
@@ -1157,8 +1151,8 @@
       <c r="H12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>129</v>
+      <c r="I12" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1186,8 +1180,8 @@
       <c r="H13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>129</v>
+      <c r="I13" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1215,8 +1209,8 @@
       <c r="H14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>129</v>
+      <c r="I14" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1244,8 +1238,8 @@
       <c r="H15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>129</v>
+      <c r="I15" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1273,8 +1267,8 @@
       <c r="H16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>129</v>
+      <c r="I16" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1302,8 +1296,8 @@
       <c r="H17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>129</v>
+      <c r="I17" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1331,8 +1325,8 @@
       <c r="H18" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>129</v>
+      <c r="I18" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1360,8 +1354,8 @@
       <c r="H19" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>129</v>
+      <c r="I19" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1389,8 +1383,8 @@
       <c r="H20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>129</v>
+      <c r="I20" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1418,8 +1412,8 @@
       <c r="H21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>129</v>
+      <c r="I21" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1447,8 +1441,8 @@
       <c r="H22" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I22" s="4" t="s">
-        <v>130</v>
+      <c r="I22" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1476,8 +1470,8 @@
       <c r="H23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>130</v>
+      <c r="I23" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1505,8 +1499,8 @@
       <c r="H24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>130</v>
+      <c r="I24" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1534,8 +1528,8 @@
       <c r="H25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="4" t="s">
-        <v>130</v>
+      <c r="I25" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1563,8 +1557,8 @@
       <c r="H26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="4" t="s">
-        <v>130</v>
+      <c r="I26" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -1592,8 +1586,8 @@
       <c r="H27" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>130</v>
+      <c r="I27" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1621,8 +1615,8 @@
       <c r="H28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>130</v>
+      <c r="I28" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1650,8 +1644,8 @@
       <c r="H29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="4" t="s">
-        <v>130</v>
+      <c r="I29" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1679,8 +1673,8 @@
       <c r="H30" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>130</v>
+      <c r="I30" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,8 +1702,8 @@
       <c r="H31" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="4" t="s">
-        <v>130</v>
+      <c r="I31" s="4">
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
